--- a/inst/extdata/ex02/User_18092019.xlsx
+++ b/inst/extdata/ex02/User_18092019.xlsx
@@ -5,11 +5,11 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Profils\mcanouil\Downloads\DATA\endoc_beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Profils\mcanouil\Downloads\DATA\endoc_beta\ex02\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Blank" sheetId="3" r:id="rId1"/>
@@ -52,12 +52,6 @@
     <t>BLANK</t>
   </si>
   <si>
-    <t>SN1</t>
-  </si>
-  <si>
-    <t>SN2</t>
-  </si>
-  <si>
     <t>Sample</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
   </si>
   <si>
     <t>Concentration (µg/L)</t>
-  </si>
-  <si>
-    <t>LYSAT</t>
   </si>
   <si>
     <t>Target</t>
@@ -140,6 +131,15 @@
   </si>
   <si>
     <t>0.5 mM Glc + A</t>
+  </si>
+  <si>
+    <t>LYSATE</t>
+  </si>
+  <si>
+    <t>SUPERNATANT1</t>
+  </si>
+  <si>
+    <t>SUPERNATANT2</t>
   </si>
 </sst>
 </file>
@@ -239,6 +239,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -465,6 +466,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -582,6 +584,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3605,13 +3608,13 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>1</v>
@@ -3620,19 +3623,19 @@
         <v>0</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -3640,10 +3643,10 @@
         <v>43726</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -3895,22 +3898,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -3919,19 +3922,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -3952,16 +3955,16 @@
         <v>CT</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>0.626799</v>
@@ -4004,16 +4007,16 @@
         <v>CT</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.65531150000000005</v>
@@ -4056,16 +4059,16 @@
         <v>CT</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.57781269999999996</v>
@@ -4108,16 +4111,16 @@
         <v>CT</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1">
         <v>0.5715787</v>
@@ -4160,16 +4163,16 @@
         <v>CT</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1">
         <v>0.52408650000000001</v>
@@ -4212,16 +4215,16 @@
         <v>CT</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1">
         <v>0.49687759999999997</v>
@@ -4264,16 +4267,16 @@
         <v>CT</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.21877579999999999</v>
@@ -4318,16 +4321,16 @@
         <v>CT</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.22155159999999999</v>
@@ -4372,16 +4375,16 @@
         <v>CT</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.2426141</v>
@@ -4426,16 +4429,16 @@
         <v>CT</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>0.31157639999999998</v>
@@ -4480,16 +4483,16 @@
         <v>CT</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I12">
         <v>0.27168799999999999</v>
@@ -4534,16 +4537,16 @@
         <v>CT</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I13">
         <v>0.24666930000000001</v>
@@ -4588,16 +4591,16 @@
         <v>CT</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.26217980000000002</v>
@@ -4642,16 +4645,16 @@
         <v>CT</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.2495522</v>
@@ -4696,16 +4699,16 @@
         <v>CT</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.25193660000000001</v>
@@ -4750,16 +4753,16 @@
         <v>CT</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1">
         <v>0.45868059999999999</v>
@@ -4804,16 +4807,16 @@
         <v>CT</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1">
         <v>0.4074757</v>
@@ -4858,16 +4861,16 @@
         <v>CT</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1">
         <v>0.30263909999999999</v>
@@ -4909,7 +4912,8 @@
     <col min="1" max="2" width="0" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="15" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
@@ -4927,22 +4931,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -4951,19 +4955,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -4984,16 +4988,16 @@
         <v>Empty</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>1.2538959999999999</v>
@@ -5036,17 +5040,17 @@
         <v>Empty</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="str">
         <f>$F$2</f>
         <v>Control</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.95461430000000003</v>
@@ -5089,17 +5093,17 @@
         <v>Empty</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="str">
         <f t="shared" ref="F4:F19" si="2">$F$2</f>
         <v>Control</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.90873990000000004</v>
@@ -5142,17 +5146,17 @@
         <v>Empty</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1">
         <v>0.8890671</v>
@@ -5195,17 +5199,17 @@
         <v>Empty</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1">
         <v>0.81566039999999995</v>
@@ -5248,17 +5252,17 @@
         <v>Empty</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1">
         <v>0.67774559999999995</v>
@@ -5301,17 +5305,17 @@
         <v>Empty</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.2334291</v>
@@ -5356,17 +5360,17 @@
         <v>Empty</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.2091017</v>
@@ -5411,17 +5415,17 @@
         <v>Empty</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.23145579999999999</v>
@@ -5466,17 +5470,17 @@
         <v>Empty</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>0.37802340000000001</v>
@@ -5521,17 +5525,17 @@
         <v>Empty</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I12">
         <v>0.31273220000000002</v>
@@ -5576,17 +5580,17 @@
         <v>Empty</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I13">
         <v>0.3950921</v>
@@ -5631,17 +5635,17 @@
         <v>Empty</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.42339830000000001</v>
@@ -5686,17 +5690,17 @@
         <v>Empty</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.3816059</v>
@@ -5741,17 +5745,17 @@
         <v>Empty</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F16" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.31764350000000002</v>
@@ -5796,17 +5800,17 @@
         <v>Empty</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1">
         <v>0.67039669999999996</v>
@@ -5851,17 +5855,17 @@
         <v>Empty</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1">
         <v>0.53370550000000005</v>
@@ -5906,17 +5910,17 @@
         <v>Empty</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Control</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1">
         <v>0.4803519</v>
@@ -5976,22 +5980,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -6000,19 +6004,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -6033,16 +6037,16 @@
         <v>GENE</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>1.0355859999999999</v>
@@ -6085,16 +6089,16 @@
         <v>GENE</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>1.1190910000000001</v>
@@ -6137,16 +6141,16 @@
         <v>GENE</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.91001900000000002</v>
@@ -6189,16 +6193,16 @@
         <v>GENE</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1">
         <v>0.92741660000000004</v>
@@ -6241,16 +6245,16 @@
         <v>GENE</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1">
         <v>0.88691779999999998</v>
@@ -6293,16 +6297,16 @@
         <v>GENE</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1">
         <v>0.64143209999999995</v>
@@ -6345,16 +6349,16 @@
         <v>GENE</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.2401431</v>
@@ -6399,16 +6403,16 @@
         <v>GENE</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.2476005</v>
@@ -6453,16 +6457,16 @@
         <v>GENE</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.22331280000000001</v>
@@ -6507,16 +6511,16 @@
         <v>GENE</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>0.39683059999999998</v>
@@ -6561,16 +6565,16 @@
         <v>GENE</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I12">
         <v>0.39607439999999999</v>
@@ -6615,16 +6619,16 @@
         <v>GENE</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I13">
         <v>0.32620710000000003</v>
@@ -6669,16 +6673,16 @@
         <v>GENE</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.34146710000000002</v>
@@ -6723,16 +6727,16 @@
         <v>GENE</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.33414460000000001</v>
@@ -6777,16 +6781,16 @@
         <v>GENE</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.31845630000000003</v>
@@ -6831,16 +6835,16 @@
         <v>GENE</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1">
         <v>0.49203330000000001</v>
@@ -6885,16 +6889,16 @@
         <v>GENE</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1">
         <v>0.58517989999999998</v>
@@ -6939,16 +6943,16 @@
         <v>GENE</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1">
         <v>0.39259189999999999</v>
